--- a/data/seed/portfolio/L-2025-5177/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-5177/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I157"/>
+  <dimension ref="A1:I171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -558,33 +558,33 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>13065000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>6010000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Navro'z Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>253186951</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000790198043001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №806 02.07.2026, QQS bilan</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №238/26</t>
         </is>
       </c>
     </row>
@@ -601,38 +601,38 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>6816000</v>
+        <v>11805000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Farg'ona Farm Savdo MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>209766819</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000328744728001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №2/26, QQS 12%</t>
+          <t>Shartnoma №295/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -641,39 +641,39 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>10580000</v>
+        <v>9308000</v>
       </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Navro'z Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>253186951</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000790198043001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4084</t>
+          <t>Оплата за товары согласно счет-фактуре №9407</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>05.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -681,40 +681,35 @@
           <t>103</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
-        <v>4610000</v>
-      </c>
+      <c r="C13" s="2" t="n">
+        <v>45800000</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>360362705</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-5177)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>16307000339219214417</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9652 03.07.2026, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-5177 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -722,40 +717,40 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>4634000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>12797000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Xiva Non MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>242753349</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000915976370001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1929</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3810</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -763,28 +758,33 @@
           <t>105</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>45800000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>11904000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-5177)</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>16307000339219214417</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-5177 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за товар по счет-фактуре №3735 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -800,32 +800,32 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>15792000</v>
+        <v>4056000</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Lazzat Metall MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>300286755</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000079537270001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №7/26, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №2846</t>
         </is>
       </c>
     </row>
@@ -841,34 +841,39 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>23516000</v>
+        <v>4119000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ISH HAQI TO'LOVI IYUN 2026 (PLASTIK KARTALARGA)</t>
+          <t>Оплата за упаковочные материалы, с/ф №9098</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -876,40 +881,40 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>13750000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>20858000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8326 07.07.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №149/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -918,39 +923,34 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>3982000</v>
+        <v>23516000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Buxoro Ip-Kalava MChJ</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>324531869</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000137901980001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №109/26</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -959,39 +959,39 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>14250000</v>
+        <v>36506000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>339002867</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000550795372001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №120/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №130/26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -999,33 +999,33 @@
           <t>111</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>5248000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>2763000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Marg'ilon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>394366588</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000539118797001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Shartnoma №200/26 bo'yicha oldindan to'lov</t>
+          <t>Ijara haqi iyul oyi uchun, shartnoma №27/24</t>
         </is>
       </c>
     </row>
@@ -1042,31 +1042,31 @@
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>4867000</v>
+        <v>3858000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №170/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №73/26, QQ 12%</t>
         </is>
       </c>
     </row>
@@ -1082,39 +1082,39 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>19313000</v>
+        <v>12105000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Navro'z Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>253186951</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000790198043001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8641</t>
+          <t>Оплата за транспортные услуги по дог. №278/26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1122,23 +1122,23 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>51645000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>5841000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oqtosh Plastik MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>322842491</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000277583058001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1148,14 +1148,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №243/26</t>
+          <t>Оплата за товар по счет-фактуре №3080 от 09.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1163,23 +1163,23 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>2763000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>40710000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jizzax Qurilish AJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>329943665</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000825391187001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartnoma №91/21</t>
+          <t>Оплата по счет-фактуре №6330 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -1206,38 +1206,38 @@
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>22751000</v>
+        <v>23962000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Non MChJ</t>
+          <t>Buxoro Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>304006940</t>
+          <t>200694005</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000530527053001</t>
+          <t>20208000052705396001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №28/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №129/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1247,31 +1247,31 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>14893000</v>
+        <v>12956000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Denov Agro Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>320721801</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000798092608001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8734 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №229/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1288,38 +1288,38 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>26649000</v>
+        <v>5403000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SHARTNOMA №290/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №15/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1327,40 +1327,40 @@
           <t>119</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>15018000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>3207000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №294/26, QQS 12%</t>
+          <t>Iyun oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1368,40 +1368,40 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>13188000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>3207000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №128/26, НДС 12%</t>
+          <t>Jismoniy shaxsar daromad solig'i iyun 2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1409,23 +1409,23 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>9231000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>9294000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barakali Poligraf MChJ</t>
+          <t>Lazzat Metall MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>327337721</t>
+          <t>300286755</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000253614502001</t>
+          <t>20208000079537270001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1435,14 +1435,14 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №263/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №207/26 от 14.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1450,23 +1450,23 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>5427000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>15867000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Buxoro Ip-Kalava MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>324531869</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000137901980001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №173/26</t>
+          <t>Shartnoma №7/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1492,39 +1492,39 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>13223000</v>
+        <v>6909000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Lazzat Metall MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>300286755</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000079537270001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №239/26</t>
+          <t>Оплата за сырье по договору №264/26 от 16.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1533,39 +1533,39 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>15500000</v>
+        <v>92472000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Lazzat Metall MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>300286755</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000079537270001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №140/26 от 13.07.2026, НДС 12%</t>
+          <t>Предоплата за материалы по договору №8/26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1573,40 +1573,40 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>18533000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>7114000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>339002867</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000550795372001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5827</t>
+          <t>Предоплата за товар по дог. №86/26 от 17.07.2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1616,38 +1616,38 @@
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>12678000</v>
+        <v>4160000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Denov Agro Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>320721801</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000798092608001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Shartnoma №254/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №220/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1655,40 +1655,40 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n">
-        <v>16145000</v>
-      </c>
+      <c r="C37" s="2" t="n">
+        <v>9167000</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>277911260</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000952439797001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №118/26, QQS 12%</t>
+          <t>Предоплата за материалы по дог. №28/26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1698,38 +1698,38 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>7370000</v>
+        <v>18033000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Andijon Mato MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>259968363</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000918446475001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №56/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №4553 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1738,39 +1738,39 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>3207000</v>
+        <v>4420000</v>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navro'z Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>253186951</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000790198043001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
+          <t>Предоплата за материалы по договору №64/26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1779,39 +1779,39 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>3207000</v>
+        <v>32757000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Metall MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>300286755</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000079537270001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Оплата за упаковочные материалы, с/ф №3147</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1819,40 +1819,40 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>6768000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>10453000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>339002867</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000550795372001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №181/26</t>
+          <t>Shartnoma №36/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1860,40 +1860,40 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>51371000</v>
-      </c>
+      <c r="C42" s="2" t="n">
+        <v>4609000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №172/26, QQS 12%</t>
+          <t>НДС а июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1901,40 +1901,40 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n">
-        <v>8975000</v>
-      </c>
+      <c r="C43" s="2" t="n">
+        <v>3543000</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Shartnoma №205/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №57/26 от 22.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1943,39 +1943,39 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>8708000</v>
+        <v>12614000</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1186</t>
+          <t>Оплата за сырье по договору №168/26 от 22.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,40 +1983,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>4641000</v>
-      </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n">
+        <v>3654000</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Buxoro Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200694005</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000052705396001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>УПЛАТА НАЛОГА НА ДОБАВЛЕННУЮ СТОИМОСТЬ ЗА ИЮНЬ</t>
+          <t>Оплата за продукцию по дог. №27/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2024,40 +2024,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>28328000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>10356000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oqtosh Plastik MChJ</t>
+          <t>Ziyo Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>322842491</t>
+          <t>396836309</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000277583058001</t>
+          <t>20208000844647519001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №143/26, QQS bilan</t>
+          <t>Shartnoma №266/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2067,38 +2067,38 @@
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>43802000</v>
+        <v>68968000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1950</t>
+          <t>Предоплата за товар по договору №75/26 от 27.07.2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2106,40 +2106,40 @@
           <t>138</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>1727000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>34719000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000732027724001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Оплата по счет-фактуре №1747 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2147,23 +2147,23 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>5072000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>12901000</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1513</t>
+          <t>Оплата за продукцию по договору №290/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2188,33 +2188,33 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>30231000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>1727000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Barakali Poligraf MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>327337721</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000253614502001</t>
+          <t>20208000202772402001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4713</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
@@ -2230,32 +2230,32 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>7962000</v>
+        <v>3313000</v>
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №165/26</t>
+          <t>Оплата за транспортные услуги по дог. №99/26</t>
         </is>
       </c>
     </row>
@@ -2271,39 +2271,39 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>10302000</v>
+        <v>5265000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9944</t>
+          <t>Оплата за товары согласно счет-фактуре №1724</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2313,38 +2313,38 @@
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>16346000</v>
+        <v>10898000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Namangan Tur Servis AJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>220427533</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000969159763001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6128</t>
+          <t>Предоплата за товар по договору №64/26 от 28.07.2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2352,23 +2352,23 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>6941000</v>
-      </c>
+      <c r="C54" s="2" t="n">
+        <v>18502000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Denov Agro Servis MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>320721801</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000798092608001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1412 29.07.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №8398</t>
         </is>
       </c>
     </row>
@@ -2394,39 +2394,39 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>55903000</v>
+        <v>4180000</v>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Navro'z Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>253186951</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000790198043001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №205/26, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №5526</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2434,33 +2434,33 @@
           <t>146</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n">
-        <v>26516000</v>
-      </c>
+      <c r="C56" s="2" t="n">
+        <v>6166000</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9590 30.07.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №150/26 от 29.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2475,40 +2475,40 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>15306000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>21123000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Xiva Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>339002867</t>
+          <t>364360694</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000550795372001</t>
+          <t>20208000574401275001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №23/26 от 30.07.2026, НДС 12%</t>
+          <t>Оплата за товар посчет-фактуре №3301 от 30.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2518,38 +2518,38 @@
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>16276000</v>
+        <v>21017000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Xiva Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>364360694</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000574401275001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №82/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №51/26 от 30.07.2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2558,27 +2558,32 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>300000</v>
+        <v>10124000</v>
       </c>
       <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №222/26 ОТ 30.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2593,40 +2598,40 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>5225000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>10049000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №205/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №143/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2636,38 +2641,38 @@
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>9086000</v>
+        <v>5501000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Andijon Mato MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>259968363</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000918446475001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Shartnoma №243/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №4768 от 31.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2675,33 +2680,28 @@
           <t>152</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>6038000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>360362705</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №93 за поставленный товар</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
     </row>
@@ -2718,31 +2718,31 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>4342000</v>
+        <v>15330000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Denov Agro Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>320721801</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000798092608001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1848</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3411 03.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -2757,33 +2757,33 @@
           <t>154</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>18486000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>3096000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9644</t>
+          <t>Mahsulot uchun to'lov, shartnoma №14/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -2799,39 +2799,39 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>21776000</v>
+        <v>1542000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Lazzat Metall MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>300286755</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000079537270001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №26/26</t>
+          <t>Оплата за сырье по дог. №175/26 от 03.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2840,34 +2840,39 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>24094000</v>
+        <v>2128000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Navro'z Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>253186951</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000790198043001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>IYUL OYI UCHUN ISH HAQI, REESTR №4971</t>
+          <t>Оплата за транспортные услуги по договору №156/26</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2876,34 +2881,39 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>45800000</v>
+        <v>4203000</v>
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-5177)</t>
+          <t>Lazzat Metall MChJ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>300286755</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>16307000339219214417</t>
+          <t>20208000079537270001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-5177 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Tovarlar uchun to'lov h/f №111</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2911,23 +2921,23 @@
           <t>158</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n">
-        <v>32956000</v>
-      </c>
+      <c r="C68" s="2" t="n">
+        <v>40695000</v>
+      </c>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Denov Agro Servis MChJ</t>
+          <t>Yulduz Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>320721801</t>
+          <t>284249152</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000798092608001</t>
+          <t>20208000758305898001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2937,14 +2947,14 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №2002 ОТ 06.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №6757</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2954,38 +2964,38 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>7514000</v>
+        <v>3972000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Ziyo Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>396836309</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000844647519001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun tolov h/f №2219</t>
+          <t>Оплата за продукцию по договору №240/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2993,40 +3003,35 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>6765000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>24094000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>360362705</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SHARTNOMA №32/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3035,39 +3040,39 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>2831000</v>
+        <v>76488000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jizzax Qurilish AJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>329943665</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000825391187001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov avgust</t>
+          <t>Оплата за товары согласно счет-фактуре №3188</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3075,40 +3080,35 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>100566000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>45800000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>360362705</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-5177)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>16307000339219214417</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №27/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2025-5177 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3118,38 +3118,38 @@
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>8502000</v>
+        <v>10808000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Samarqand Tekstil MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>376681923</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000874472880001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №290/26, QQS 12%</t>
+          <t>Shartnoma №18/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3157,40 +3157,40 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>5425000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>2170000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Buxoro Ip-Kalava MChJ</t>
+          <t>Buxoro Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>324531869</t>
+          <t>200694005</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000137901980001</t>
+          <t>20208000052705396001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №108/26, QQS bilan</t>
+          <t>Shartnoma №231/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3199,39 +3199,39 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>38328000</v>
+        <v>1533000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Yulduz Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>284249152</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000758305898001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за ырье по договору №2/26 от 11.08.2026, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №50/26</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3241,38 +3241,38 @@
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>21053000</v>
+        <v>2360000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Shartnoma №274/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №6947 от 07.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3280,40 +3280,40 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>7785000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>2831000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Denov Agro Servis MChJ</t>
+          <t>Marg'ilon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>320721801</t>
+          <t>394366588</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000798092608001</t>
+          <t>20208000539118797001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9975 14.08.2026, QQS bilan</t>
+          <t>Арендная плата за август 2026 г. по договору №27/24</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3321,40 +3321,40 @@
           <t>168</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>35055000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>12859000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №50/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №9808</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3362,40 +3362,40 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>3286000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>2632000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ziyo Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>396836309</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000844647519001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Tovar uchun to'lov, hisob-faktura №940 10.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3404,39 +3404,39 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>3286000</v>
+        <v>8471000</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Metall MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>300286755</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000079537270001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №9398</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3444,40 +3444,40 @@
           <t>171</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>7745000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>5003000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>339002867</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000550795372001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №153/26</t>
+          <t>Предоплата за товар по договору №278/26 от 11.08.2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3486,39 +3486,39 @@
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>8759000</v>
+        <v>114071000</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Lazzat Metall MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>300286755</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000079537270001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №165/26</t>
+          <t>Оплата за транспортные услуги по дог. №169/26</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,40 +3526,40 @@
           <t>173</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>14712000</v>
-      </c>
-      <c r="D83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n">
+        <v>113222000</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oqtosh Plastik MChJ</t>
+          <t>Buxoro Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>322842491</t>
+          <t>200694005</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000277583058001</t>
+          <t>20208000052705396001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №503</t>
+          <t>Предоплата за товар по договору №249/26 от 12.08.2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3569,38 +3569,38 @@
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>14348000</v>
+        <v>4420000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №185/26, НДС 12%</t>
+          <t>Оплата за продуцию по дог. №11/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3608,40 +3608,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>6668000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>3640000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Ishonch Poligraf XK</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>391126089</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000243979776001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №193/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №174/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3651,38 +3651,38 @@
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>8754000</v>
+        <v>51288000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6334</t>
+          <t>Оплата за товар по счет-фактуре №2794 от 14.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3690,40 +3690,40 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>23779000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>3838000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Shartnoma №187/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №189/26</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3732,39 +3732,39 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>16130000</v>
+        <v>11663000</v>
       </c>
       <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>339002867</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000550795372001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №23/26, QQS ILAN</t>
+          <t>Tovarlar uchun to'lov h/f №6549</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3773,39 +3773,39 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>1770000</v>
+        <v>13695000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000732027724001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за сырье по договору №8/26 от 14.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3813,40 +3813,40 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>4844000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>95170000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Оплата за продукцию по дог. №93/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3854,40 +3854,40 @@
           <t>181</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n">
-        <v>18967000</v>
-      </c>
-      <c r="D91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n">
+        <v>11120000</v>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Ziyo Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>339002867</t>
+          <t>396836309</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000550795372001</t>
+          <t>20208000844647519001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №83/26, QQS bilan</t>
+          <t>Shartnoma №227/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3895,23 +3895,23 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>31120000</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n">
+        <v>8388000</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Xiva Non MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>339002867</t>
+          <t>242753349</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000550795372001</t>
+          <t>20208000915976370001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №77</t>
+          <t>Оплата за товар по с/ф №4512 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3937,39 +3937,39 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>50963000</v>
+        <v>3286000</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>339002867</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000550795372001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №196/26</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3977,40 +3977,40 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n">
-        <v>83607000</v>
-      </c>
+      <c r="C94" s="2" t="n">
+        <v>3286000</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7275</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4019,39 +4019,39 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>15267000</v>
+        <v>11956000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>339002867</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000550795372001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №46/26, QQS bilan</t>
+          <t>Оплата за сырье по договору №243/26 от 18.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4059,40 +4059,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>17038000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>10350000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oqtosh Plastik MChJ</t>
+          <t>Ziyo Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>322842491</t>
+          <t>396836309</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000277583058001</t>
+          <t>20208000844647519001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1082</t>
+          <t>Оплата за товар по счет-фактуре №767 от 20.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4100,40 +4100,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>42490000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>4488000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Ishonch Poligraf XK</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>391126089</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000243979776001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8807</t>
+          <t>Оплата по счет-фактуре №8354 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4143,38 +4143,38 @@
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>9244000</v>
+        <v>2493000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Denov Agro Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>320721801</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000798092608001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7579</t>
+          <t>Оплата за продукцию по дог. №296/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4184,38 +4184,38 @@
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>7134000</v>
+        <v>4697000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4460</t>
+          <t>Предоплата за товар по договору №202/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4225,38 +4225,38 @@
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>5183000</v>
+        <v>3138000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №120/26 от 27.08.2026</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №284/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4266,38 +4266,38 @@
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>11914000</v>
+        <v>2242000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Shartnoma №282/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №186/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4306,34 +4306,39 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>300000</v>
+        <v>3193000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Lazzat Metall MChJ</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>300286755</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000079537270001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата за товары согласно счет-фактуре №3585</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4341,40 +4346,40 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>196828000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>4730000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Dori-Darmon AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>345643606</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000485744012001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2658 02.09.2026, QQS bilan</t>
+          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4382,40 +4387,40 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>4088000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>1770000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Non MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>304006940</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000530527053001</t>
+          <t>20208000202772402001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №393 02.09.2026, QQS bilan</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4423,23 +4428,23 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>22643000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>3195000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Oqtosh Plastik MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>322842491</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000277583058001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4449,14 +4454,14 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTN. №136/26</t>
+          <t>Оплата з товар по счет-фактуре №5641 от 26.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4464,40 +4469,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>6761000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>2816000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9554 03.09.2026, QQS ilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №1601</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4505,40 +4510,40 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>14903000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>15227000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Buxoro Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>200694005</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000052705396001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №140/26</t>
+          <t>Оплата по счет-фактуре №2881 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4546,35 +4551,40 @@
           <t>198</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>23680000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>11838000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №7175</t>
+          <t>Оплата по счет-фактуре №3900 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4582,35 +4592,40 @@
           <t>199</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>45800000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>3907000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-5177)</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>16307000339219214417</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-5177 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата за товар по счет-фактуре №784 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4618,40 +4633,35 @@
           <t>200</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>5106000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>360362705</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5096</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4659,23 +4669,23 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>2783000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>2733000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Jizzax Qurilish AJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>329943665</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000825391187001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4685,14 +4695,14 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №91/21</t>
+          <t>ОПЛАТА ПО С/Ф №279 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4701,39 +4711,39 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>22296000</v>
+        <v>4609000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Buxoro Ip-Kalava MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>324531869</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000137901980001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №253/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №8278</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4741,23 +4751,23 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>32496000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>3351000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Oqtosh Plastik MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>322842491</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000277583058001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4767,14 +4777,14 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №5010</t>
+          <t>Оплата за продукцию по договору №127/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4784,38 +4794,38 @@
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>10644000</v>
+        <v>11329000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №289/26, QQS 12%</t>
+          <t>Оплата по с/ф №3427 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4825,38 +4835,38 @@
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>4198000</v>
+        <v>3245000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shrtnoma №277/26, QQS 12%</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №254/26 ОТ 04.09.2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>05.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4864,40 +4874,35 @@
           <t>206</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n">
-        <v>4238000</v>
-      </c>
+      <c r="C116" s="2" t="n">
+        <v>45800000</v>
+      </c>
+      <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>360362705</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-5177)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>16307000339219214417</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5839</t>
+          <t>Kredit shartnomasi L-2025-5177 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4907,38 +4912,38 @@
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>2391000</v>
+        <v>9400000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №17/26, QQS 12%</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №5010 07.09.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4948,38 +4953,38 @@
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>2080000</v>
+        <v>3554000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Andijon Mato MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>259968363</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000918446475001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6540 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по с/ф №9267 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4989,38 +4994,38 @@
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>11691000</v>
+        <v>3458000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Non MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>304006940</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000530527053001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №9/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №5816 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5028,40 +5033,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>7918000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>12079000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №3374 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №5578</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5070,39 +5075,39 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>3229000</v>
+        <v>19437000</v>
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ijtimoiy soliq</t>
+          <t>Оплата за упаковочные материалы, с/ф №9952</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5111,39 +5116,34 @@
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>3229000</v>
+        <v>23680000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август2026 г.</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №3912</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5152,39 +5152,39 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>23420000</v>
+        <v>2783000</v>
       </c>
       <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Buxoro Ip-Kalava MChJ</t>
+          <t>Marg'ilon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>324531869</t>
+          <t>394366588</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000137901980001</t>
+          <t>20208000539118797001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за транспортне услуги по договору №248/26</t>
+          <t>Аренда помещения за сентябрь, дог. №27/24</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5192,40 +5192,40 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>23574000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>4476000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8576</t>
+          <t>Оплата за продукцию по договору №94/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5235,38 +5235,38 @@
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>2399000</v>
+        <v>2804000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5106 за поставленный товар</t>
+          <t>Предоплата за товар по договору №269/26 от 09.09.2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5274,40 +5274,40 @@
           <t>216</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>2036000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>4174000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Non MChJ</t>
+          <t>Navro'z Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>304006940</t>
+          <t>253186951</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000530527053001</t>
+          <t>20208000790198043001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №90/26 от 17.09.2026</t>
+          <t>Предоплата за материалы по договору №249/26</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5315,40 +5315,40 @@
           <t>217</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>3750000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>48777000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Non MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>304006940</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000530527053001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №86/26 от 18.09.2026</t>
+          <t>Оплата а сырье по договору №48/26 от 10.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5358,38 +5358,38 @@
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>6812000</v>
+        <v>3096000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1840 21.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №20/26 от 11.09.2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5397,40 +5397,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>3346000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>13032000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Shartnoma №74/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно счет-фактуре №7462</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5440,38 +5440,38 @@
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>1993000</v>
+        <v>27795000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2483</t>
+          <t>Shartnoma №215/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5479,40 +5479,40 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>4597000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>20038000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
+          <t>Оплата за товар по счет-фактуре №2378 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5522,38 +5522,38 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>13645000</v>
+        <v>17152000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Denov Agro Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>320721801</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000798092608001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №173/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №3834 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5563,38 +5563,38 @@
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>4394000</v>
+        <v>16610000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Farg'ona Polimer MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>333772162</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000361450261001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №9778 22.09.2026, QQS BILAN</t>
+          <t>Mahsulot uchun to'lov, shartnoma №194/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5602,40 +5602,40 @@
           <t>224</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>4123000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>3229000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №43/26, QQS 12%</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5643,40 +5643,40 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>2711000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>3229000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Andijon Mato MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>259968363</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000918446475001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Shartnoma №151/26 bo'yicha oldindan to'lov</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5685,22 +5685,22 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>75524000</v>
+        <v>7872000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Lazzat Metall MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>339002867</t>
+          <t>300286755</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000550795372001</t>
+          <t>20208000079537270001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5710,14 +5710,14 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lo, shartn. №230/26, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №47/26</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5725,23 +5725,23 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>20054000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>27422000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5751,14 +5751,14 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №228/26</t>
+          <t>Оплата за товар по с/ф №6566 от 15.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5768,38 +5768,38 @@
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>12546000</v>
+        <v>13858000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov shartnoma №59/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №57/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5809,38 +5809,38 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>5777000</v>
+        <v>11477000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3133 25.09.2026, QQS bilan</t>
+          <t>Yetkazilgan tova uchun to'lov h/f №4727</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5850,38 +5850,38 @@
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>3967000</v>
+        <v>7540000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №235/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1636 15.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5890,39 +5890,39 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>14979000</v>
+        <v>5555000</v>
       </c>
       <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Yulduz Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>284249152</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000758305898001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №106/26, QQS bilan</t>
+          <t>Предоплата за материалы по дог. №238/26</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5932,38 +5932,38 @@
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>22457000</v>
+        <v>17505000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Denov Agro Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>320721801</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000798092608001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7657 28.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №196/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5973,38 +5973,38 @@
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>15404000</v>
+        <v>10984000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Ishonch Metall MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>272180177</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000809260806001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Shartnoma №246/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №275/26 от 18.09.2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6014,38 +6014,38 @@
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>3796000</v>
+        <v>6621000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №564 28.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №52/26 от 18.09.2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6053,40 +6053,40 @@
           <t>235</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>3573000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>10602000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Navro'z Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>253186951</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000790198043001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9495</t>
+          <t>Оплата за товары согласно счет-фактуре №3843</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6096,21 +6096,21 @@
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>3072000</v>
+        <v>5748000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Buxoro Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>200694005</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000052705396001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6120,14 +6120,14 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3661 28.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №229/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6135,40 +6135,40 @@
           <t>237</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>2166000</v>
-      </c>
+      <c r="C147" s="2" t="n">
+        <v>12239000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Shartnoma №246/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно с/ф №1680</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6176,23 +6176,23 @@
           <t>238</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>2165000</v>
-      </c>
+      <c r="C148" s="2" t="n">
+        <v>72153000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Barakali Poligraf MChJ</t>
+          <t>Lazzat Metall MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>327337721</t>
+          <t>300286755</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000253614502001</t>
+          <t>20208000079537270001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6202,14 +6202,14 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №7377</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №8307</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6219,38 +6219,38 @@
       </c>
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="n">
-        <v>2061000</v>
+        <v>9929000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Yangi Hayot Metall Servis MChJ</t>
+          <t>Ziyo Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>360362705</t>
+          <t>396836309</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000264197828001</t>
+          <t>20208000844647519001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8353 28.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №174/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6258,40 +6258,40 @@
           <t>240</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n">
-        <v>1739000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>4105000</v>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Farg'ona Polimer MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>333772162</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000732027724001</t>
+          <t>20208000361450261001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+          <t>Оплата за товар по с/ф №847 от 23.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6299,23 +6299,23 @@
           <t>241</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n">
-        <v>13554000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>3873000</v>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Qo'qon Tur Servis MChJ</t>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>339002867</t>
+          <t>236270542</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000550795372001</t>
+          <t>20208000419782859001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6325,14 +6325,14 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №122/26</t>
+          <t>Оплата по счет-фактуре №2165 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6341,39 +6341,39 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>21396000</v>
+        <v>1739000</v>
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000202772402001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5869</t>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6381,40 +6381,40 @@
           <t>243</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>4910000</v>
-      </c>
+      <c r="C153" s="2" t="n">
+        <v>4569000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Farg'ona Farm Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>209766819</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000328744728001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Shartnoma №18/26 bo'yicha oldindan to'lov</t>
+          <t>НДС за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6423,39 +6423,39 @@
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>30813000</v>
+        <v>17511000</v>
       </c>
       <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo XK</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>220869040</t>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000487413668001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №299/26, QQS bilan</t>
+          <t>Оплата за сырье по дог. №69/26 от 23.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6464,53 +6464,627 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>300000</v>
+        <v>57057000</v>
       </c>
       <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Urganch Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>286904084</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000741366805001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата за товары согласно счет-фактуре №8531</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="n">
-        <v>1202708000</v>
-      </c>
-      <c r="D156" s="4" t="n">
-        <v>1173408000</v>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>62285000</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>236270542</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000419782859001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>SHARTNOMA №26/26 BO'YICHA OLDINDAN TO'LOV</t>
+        </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>3572000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>236270542</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000419782859001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6161</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>11048000</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>236270542</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000419782859001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №4001 25.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>7432000</v>
+      </c>
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Navro'z Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>253186951</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000790198043001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно с/ф №6210</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>12847000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Urganch Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>286904084</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000741366805001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №9666</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>7154000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>236270542</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000419782859001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №244/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>5582000</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Buxoro Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>200694005</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000052705396001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №101/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>2870000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Xiva Non MChJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>242753349</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000915976370001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №122/26 от 28.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>2772000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>236270542</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000419782859001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №8472 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n">
+        <v>21724000</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>236270542</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000419782859001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №7081 от 29.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n">
+        <v>10062000</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Samarqand Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>376681923</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000874472880001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №6840 29.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>5580000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Sarbon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>236270542</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000419782859001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №110/26 от 29.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Navbahor Bank ATB</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Плата за SMS-информирование</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>5525000</v>
+      </c>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Urganch Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>286904084</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000741366805001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по дог. №293/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="n">
+        <v>1188295000</v>
+      </c>
+      <c r="D170" s="4" t="n">
+        <v>1158995000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C157" s="4" t="n">
+      <c r="C171" s="4" t="n">
         <v>170900000</v>
       </c>
-      <c r="D157" s="4" t="n"/>
+      <c r="D171" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
